--- a/evaluation_forms/029_draft_gcs_reporting_form--evaluation_forms.xlsx
+++ b/evaluation_forms/029_draft_gcs_reporting_form--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -646,24 +646,24 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>email_2</t>
+          <t>assigned_technician_2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Second Assigned Technician</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>report_date_2</t>
+          <t>phone_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Report Date</t>
+          <t>Second Phone</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assigned_technician_2</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assigned Technician</t>
+          <t>Second Email</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>draft_gcs_reporting_form_comments_2</t>
+          <t>report_date_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Second Report Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>phone_2</t>
+          <t>draft_gcs_reporting_form_comments_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Second Comments</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>report_date_3</t>
+          <t>assigned_technician_3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Report Date</t>
+          <t>Third Assigned Technician</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,17 +791,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>draft_gcs_reporting_form_comments_3</t>
+          <t>phone_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Third Phone</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,17 +814,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>assigned_technician_3</t>
+          <t>email_3</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Assigned Technician</t>
+          <t>Third Email</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>phone_3</t>
+          <t>report_date_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Third Report Date</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>email_2</t>
+          <t>draft_gcs_reporting_form_comments_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Third Comments</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>report_date_4</t>
+          <t>assigned_technician_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Report Date</t>
+          <t>Fourth Assigned Technician</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>email_3</t>
+          <t>phone_4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Fourth Phone</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,21 +929,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>assigned_technician_4</t>
+          <t>email_4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Assigned Technician</t>
+          <t>Fourth Email</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>report_date_4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Fourth Report Date</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
         <is>
           <t>no</t>
         </is>
